--- a/outputs/q4/q4_relay_policy_sensitivity.xlsx
+++ b/outputs/q4/q4_relay_policy_sensitivity.xlsx
@@ -572,14 +572,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S001|S002,S003,S004,S005,S006,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015|S006</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -591,25 +591,25 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9029098128200543</v>
+        <v>0.8825900780064836</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
@@ -618,7 +618,7 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -657,25 +657,25 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.190790358782802</v>
+        <v>1.183290165105396</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
         <v>2</v>
@@ -684,7 +684,7 @@
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -704,14 +704,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S001|S002,S003,S004,S005,S006,S007,S008,S009,S010,S011,S012,S013,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S011,S012,S013,S014,S015|S006</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9029098128200543</v>
+        <v>0.8825900780064836</v>
       </c>
       <c r="O4" t="n">
         <v>28</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
         <v>4</v>
@@ -750,7 +750,7 @@
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -789,25 +789,25 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N5" t="n">
-        <v>1.190790358782802</v>
+        <v>1.183290165105396</v>
       </c>
       <c r="O5" t="n">
         <v>89</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R5" t="n">
         <v>6</v>
@@ -816,7 +816,7 @@
         <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
